--- a/outputs/table/table2_auc_delong_summary.xlsx
+++ b/outputs/table/table2_auc_delong_summary.xlsx
@@ -61,151 +61,151 @@
     <t>B: +VAT+SAT</t>
   </si>
   <si>
-    <t>0.808</t>
-  </si>
-  <si>
-    <t>0.714</t>
-  </si>
-  <si>
-    <t>0.727</t>
-  </si>
-  <si>
-    <t>0.662</t>
-  </si>
-  <si>
-    <t>0.792</t>
-  </si>
-  <si>
-    <t>0.621</t>
-  </si>
-  <si>
-    <t>0.813</t>
-  </si>
-  <si>
-    <t>0.818</t>
-  </si>
-  <si>
-    <t>0.719</t>
-  </si>
-  <si>
-    <t>0.729</t>
-  </si>
-  <si>
-    <t>0.726</t>
-  </si>
-  <si>
-    <t>0.731</t>
-  </si>
-  <si>
-    <t>0.663</t>
-  </si>
-  <si>
-    <t>0.674</t>
-  </si>
-  <si>
-    <t>0.798</t>
-  </si>
-  <si>
-    <t>0.806</t>
-  </si>
-  <si>
-    <t>0.613</t>
+    <t>0.794</t>
+  </si>
+  <si>
+    <t>0.718</t>
+  </si>
+  <si>
+    <t>0.722</t>
+  </si>
+  <si>
+    <t>0.665</t>
+  </si>
+  <si>
+    <t>0.768</t>
+  </si>
+  <si>
+    <t>0.616</t>
+  </si>
+  <si>
+    <t>0.796</t>
+  </si>
+  <si>
+    <t>0.811</t>
+  </si>
+  <si>
+    <t>0.730</t>
+  </si>
+  <si>
+    <t>0.721</t>
+  </si>
+  <si>
+    <t>0.723</t>
+  </si>
+  <si>
+    <t>0.677</t>
+  </si>
+  <si>
+    <t>0.770</t>
+  </si>
+  <si>
+    <t>0.614</t>
+  </si>
+  <si>
+    <t>0.617</t>
+  </si>
+  <si>
+    <t>0.802</t>
+  </si>
+  <si>
+    <t>0.810</t>
+  </si>
+  <si>
+    <t>0.733</t>
+  </si>
+  <si>
+    <t>0.741</t>
+  </si>
+  <si>
+    <t>0.735</t>
+  </si>
+  <si>
+    <t>0.681</t>
+  </si>
+  <si>
+    <t>0.686</t>
+  </si>
+  <si>
+    <t>0.772</t>
+  </si>
+  <si>
+    <t>0.773</t>
+  </si>
+  <si>
+    <t>0.630</t>
+  </si>
+  <si>
+    <t>0.626</t>
+  </si>
+  <si>
+    <t>0.454</t>
+  </si>
+  <si>
+    <t>0.005</t>
+  </si>
+  <si>
+    <t>0.835</t>
+  </si>
+  <si>
+    <t>0.086</t>
+  </si>
+  <si>
+    <t>0.073</t>
   </si>
   <si>
     <t>0.820</t>
   </si>
   <si>
-    <t>0.734</t>
-  </si>
-  <si>
-    <t>0.748</t>
-  </si>
-  <si>
-    <t>0.746</t>
-  </si>
-  <si>
-    <t>0.699</t>
-  </si>
-  <si>
-    <t>0.809</t>
-  </si>
-  <si>
-    <t>0.811</t>
-  </si>
-  <si>
-    <t>0.643</t>
-  </si>
-  <si>
-    <t>0.637</t>
-  </si>
-  <si>
-    <t>0.104</t>
-  </si>
-  <si>
-    <t>0.058</t>
-  </si>
-  <si>
-    <t>0.208</t>
-  </si>
-  <si>
-    <t>0.018</t>
-  </si>
-  <si>
-    <t>0.853</t>
-  </si>
-  <si>
-    <t>0.474</t>
-  </si>
-  <si>
-    <t>0.710</t>
-  </si>
-  <si>
-    <t>0.055</t>
-  </si>
-  <si>
-    <t>0.341</t>
-  </si>
-  <si>
-    <t>0.230</t>
-  </si>
-  <si>
-    <t>0.126</t>
-  </si>
-  <si>
-    <t>0.958</t>
-  </si>
-  <si>
-    <t>0.245</t>
-  </si>
-  <si>
-    <t>0.537</t>
-  </si>
-  <si>
-    <t>0.011</t>
-  </si>
-  <si>
-    <t>0.193</t>
-  </si>
-  <si>
-    <t>0.013</t>
-  </si>
-  <si>
-    <t>0.048</t>
-  </si>
-  <si>
-    <t>&lt;0.001</t>
-  </si>
-  <si>
-    <t>0.002</t>
-  </si>
-  <si>
-    <t>0.315</t>
-  </si>
-  <si>
-    <t>0.615</t>
-  </si>
-  <si>
-    <t>0.036</t>
+    <t>0.953</t>
+  </si>
+  <si>
+    <t>0.112</t>
+  </si>
+  <si>
+    <t>0.787</t>
+  </si>
+  <si>
+    <t>0.782</t>
+  </si>
+  <si>
+    <t>0.359</t>
+  </si>
+  <si>
+    <t>0.156</t>
+  </si>
+  <si>
+    <t>0.912</t>
+  </si>
+  <si>
+    <t>0.020</t>
+  </si>
+  <si>
+    <t>0.261</t>
+  </si>
+  <si>
+    <t>0.012</t>
+  </si>
+  <si>
+    <t>0.050</t>
+  </si>
+  <si>
+    <t>0.070</t>
+  </si>
+  <si>
+    <t>0.181</t>
+  </si>
+  <si>
+    <t>0.592</t>
+  </si>
+  <si>
+    <t>0.657</t>
+  </si>
+  <si>
+    <t>0.007</t>
+  </si>
+  <si>
+    <t>0.079</t>
   </si>
 </sst>
 </file>
@@ -609,13 +609,13 @@
         <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="G2" t="s">
         <v>41</v>
       </c>
       <c r="H2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -635,13 +635,13 @@
         <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G3" t="s">
         <v>42</v>
       </c>
       <c r="H3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -658,16 +658,16 @@
         <v>16</v>
       </c>
       <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s">
         <v>23</v>
-      </c>
-      <c r="F4" t="s">
-        <v>26</v>
       </c>
       <c r="G4" t="s">
         <v>43</v>
       </c>
       <c r="H4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -684,16 +684,16 @@
         <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G5" t="s">
         <v>44</v>
       </c>
       <c r="H5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -710,16 +710,16 @@
         <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G6" t="s">
         <v>45</v>
       </c>
       <c r="H6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -736,16 +736,16 @@
         <v>17</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G7" t="s">
         <v>46</v>
       </c>
       <c r="H7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -762,16 +762,16 @@
         <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G8" t="s">
         <v>47</v>
       </c>
       <c r="H8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -788,7 +788,7 @@
         <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F9" t="s">
         <v>36</v>
@@ -797,7 +797,7 @@
         <v>48</v>
       </c>
       <c r="H9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -814,7 +814,7 @@
         <v>19</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F10" t="s">
         <v>37</v>
@@ -823,7 +823,7 @@
         <v>49</v>
       </c>
       <c r="H10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -840,7 +840,7 @@
         <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F11" t="s">
         <v>38</v>
@@ -849,7 +849,7 @@
         <v>50</v>
       </c>
       <c r="H11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -866,7 +866,7 @@
         <v>20</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F12" t="s">
         <v>39</v>
@@ -875,7 +875,7 @@
         <v>51</v>
       </c>
       <c r="H12" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -892,13 +892,13 @@
         <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F13" t="s">
         <v>40</v>
       </c>
       <c r="G13" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H13" t="s">
         <v>63</v>
